--- a/TestData/TMTT0009535_TMTC0001544_TMTC0001548_TMTI0045473_TMTI0045475_VerifyRateGenerationToStaffWithDifferentTitleInSummaryAndDetailsLogTab.xlsx
+++ b/TestData/TMTT0009535_TMTC0001544_TMTC0001548_TMTI0045473_TMTI0045475_VerifyRateGenerationToStaffWithDifferentTitleInSummaryAndDetailsLogTab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AE3B2F-F9D4-42DB-BE90-DD9ACF34AA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662B353C-F0FA-47AD-83C0-8DFD317255DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1620" yWindow="1968" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -19,10 +19,21 @@
     <sheet name="RateSheetManagement" sheetId="9" r:id="rId4"/>
     <sheet name="StaffMember" sheetId="10" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -88,67 +99,67 @@
     <t>175</t>
   </si>
   <si>
+    <t>Aaron Matthew Tsing Yinn Chinn</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>400.00</t>
+  </si>
+  <si>
+    <t>95.00</t>
+  </si>
+  <si>
+    <t>Terence Tchen</t>
+  </si>
+  <si>
+    <t>Senior Advisor</t>
+  </si>
+  <si>
+    <t>1,000</t>
+  </si>
+  <si>
+    <t>1,000.00</t>
+  </si>
+  <si>
+    <t>DefaultRateForAdminwithoutRatedSheetadded</t>
+  </si>
+  <si>
+    <t>DefaultRateForAdminwithRatedSheetadded</t>
+  </si>
+  <si>
+    <t>.00</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>(MEH) Thompson_CLP Toxicology-Thompson Hine, LLP-FVA-26495</t>
+  </si>
+  <si>
+    <t>Debevoise_Xie (Consulting)-Debevoise &amp; Plimpton LLP-FVA-26378</t>
+  </si>
+  <si>
+    <t>(GB) Anthony_ACOVA-Anthony Ostlund Baer &amp; Louwagie P.A.-FVA-27471</t>
+  </si>
+  <si>
+    <t>Eventide-Eventide Asset Management, LLC-FVA-111771</t>
+  </si>
+  <si>
+    <t>DRC - Original</t>
+  </si>
+  <si>
     <t>Rahimeh Bahrampourian</t>
   </si>
   <si>
     <t>Salesforce Administrator</t>
-  </si>
-  <si>
-    <t>Aaron Matthew Tsing Yinn Chinn</t>
-  </si>
-  <si>
-    <t>Financial Analyst</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>400.00</t>
-  </si>
-  <si>
-    <t>95.00</t>
-  </si>
-  <si>
-    <t>Terence Tchen</t>
-  </si>
-  <si>
-    <t>Senior Advisor</t>
-  </si>
-  <si>
-    <t>1,000</t>
-  </si>
-  <si>
-    <t>1,000.00</t>
-  </si>
-  <si>
-    <t>DefaultRateForAdminwithoutRatedSheetadded</t>
-  </si>
-  <si>
-    <t>DefaultRateForAdminwithRatedSheetadded</t>
-  </si>
-  <si>
-    <t>.00</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>(MEH) Thompson_CLP Toxicology-Thompson Hine, LLP-FVA-26495</t>
-  </si>
-  <si>
-    <t>Debevoise_Xie (Consulting)-Debevoise &amp; Plimpton LLP-FVA-26378</t>
-  </si>
-  <si>
-    <t>(GB) Anthony_ACOVA-Anthony Ostlund Baer &amp; Louwagie P.A.-FVA-27471</t>
-  </si>
-  <si>
-    <t>Eventide-Eventide Asset Management, LLC-FVA-111771</t>
-  </si>
-  <si>
-    <t>DRC - Original</t>
   </si>
 </sst>
 </file>
@@ -486,18 +497,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -511,17 +522,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -532,18 +543,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -552,18 +563,18 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -578,12 +589,12 @@
         <v>5</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -592,18 +603,18 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -612,13 +623,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -630,16 +641,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -650,15 +661,15 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
@@ -667,15 +678,15 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
@@ -687,12 +698,12 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -701,15 +712,15 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -718,10 +729,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -733,14 +744,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -748,36 +759,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -789,13 +800,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -806,18 +817,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3">
         <v>983</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -828,23 +839,23 @@
         <v>752</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
